--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T09:16:42+00:00</t>
+    <t>2026-04-20T07:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:14:21+00:00</t>
+    <t>2026-04-20T13:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:39:43+00:00</t>
+    <t>2026-04-20T13:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:49:18+00:00</t>
+    <t>2026-04-20T13:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:52:11+00:00</t>
+    <t>2026-04-20T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:01:02+00:00</t>
+    <t>2026-04-20T14:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:11:31+00:00</t>
+    <t>2026-04-20T14:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-Document.xlsx
+++ b/main/ig/StructureDefinition-Document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:36:06+00:00</t>
+    <t>2026-04-20T14:56:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
